--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1641,9 +1641,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF8F15F0-888E-4D04-AD00-454D6435A95A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A976D010-77B2-4D35-AD40-3353A59A882E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C22B04-8B0E-4D1D-A6A7-A197904943AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5021C243-AAA2-473D-9804-98ECC2131B92}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1377,8 +1377,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -1640,10 +1640,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A976D010-77B2-4D35-AD40-3353A59A882E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2F3806-86A6-419C-9C92-7B8201D7EACB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5021C243-AAA2-473D-9804-98ECC2131B92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B3EB5F-C33F-4B52-9A62-53611E8973D9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE3DC54-982C-4F2F-90A4-25D6ABDA2D77}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2F3806-86A6-419C-9C92-7B8201D7EACB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191B79B0-E809-4E02-BE88-30E806448254}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B3EB5F-C33F-4B52-9A62-53611E8973D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E57774B8-777C-4158-AD23-CA618C55DE19}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE3DC54-982C-4F2F-90A4-25D6ABDA2D77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DBA6949-E895-47BD-800C-9F64F02619F9}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191B79B0-E809-4E02-BE88-30E806448254}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1490D9CD-D75D-4855-8808-5F9314223D26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E57774B8-777C-4158-AD23-CA618C55DE19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09927AFC-6A02-4591-A704-6623E9CB2253}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DBA6949-E895-47BD-800C-9F64F02619F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C039567-3FAC-44DB-A3CB-E394F55154D2}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1490D9CD-D75D-4855-8808-5F9314223D26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688723F3-BCD7-449B-B306-98955320DB4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09927AFC-6A02-4591-A704-6623E9CB2253}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45F770A0-C0D1-4E72-B6F7-5140BC0BC603}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C039567-3FAC-44DB-A3CB-E394F55154D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4B2B246-E8C9-41B0-BAE7-EA5F4DC5D776}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{688723F3-BCD7-449B-B306-98955320DB4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CC5D29-B76F-409B-820B-03EF56758227}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45F770A0-C0D1-4E72-B6F7-5140BC0BC603}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779C7BBB-13F6-467E-8ED2-560B828423C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4B2B246-E8C9-41B0-BAE7-EA5F4DC5D776}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEE12C4-30A3-4A79-83F6-ACC02505628F}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CC5D29-B76F-409B-820B-03EF56758227}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09738B89-CFEA-4562-AE39-C39D3858EEA0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779C7BBB-13F6-467E-8ED2-560B828423C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AEE0A42-C63F-4A76-AA2E-89F997EA1A02}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEE12C4-30A3-4A79-83F6-ACC02505628F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB6B650-7D24-4E6A-93AB-1C8763F1315F}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09738B89-CFEA-4562-AE39-C39D3858EEA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A596A9B1-CB1D-491C-BA23-024BF7D7934F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AEE0A42-C63F-4A76-AA2E-89F997EA1A02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FC4183B-AF9E-452E-9CDE-149DEFF8C458}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAB6B650-7D24-4E6A-93AB-1C8763F1315F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4144936D-F4E1-4621-9FC0-8015EDF28B26}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A596A9B1-CB1D-491C-BA23-024BF7D7934F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1945B346-BB15-4294-95CE-9CB1D062D470}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FC4183B-AF9E-452E-9CDE-149DEFF8C458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9FEAEA-006C-45D8-A57B-9893A1C4238A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4144936D-F4E1-4621-9FC0-8015EDF28B26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4D659CA-CA81-4F10-98B7-EC06C76DA7C9}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1945B346-BB15-4294-95CE-9CB1D062D470}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{016B77F3-71F7-427C-9D28-87AF242CBC4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9FEAEA-006C-45D8-A57B-9893A1C4238A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCB746E1-9BAD-49F9-8064-5FFFCBACCD28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4D659CA-CA81-4F10-98B7-EC06C76DA7C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A199A3D3-6493-4593-877B-4E4819914420}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{016B77F3-71F7-427C-9D28-87AF242CBC4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E170C57-4A6E-4A64-BEF9-928F047F35CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCB746E1-9BAD-49F9-8064-5FFFCBACCD28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{871C8D03-BB0F-49CF-8B07-9DF8589B1987}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A199A3D3-6493-4593-877B-4E4819914420}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04074C78-BF5A-413C-93EB-66EE557EE587}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E170C57-4A6E-4A64-BEF9-928F047F35CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A344B8BD-A1F6-4BFD-A57B-13A08A395DFA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{871C8D03-BB0F-49CF-8B07-9DF8589B1987}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C94329F-874D-45C5-B2B7-502C086586BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04074C78-BF5A-413C-93EB-66EE557EE587}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E9600A-D48D-4E43-A0F3-D2A586D167FE}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A344B8BD-A1F6-4BFD-A57B-13A08A395DFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06472E9B-E389-4096-BBBD-4F84E745F017}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C94329F-874D-45C5-B2B7-502C086586BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B166806-E1BA-4662-AAAA-802A0E38DF76}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E9600A-D48D-4E43-A0F3-D2A586D167FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F279D038-D31F-4728-9633-DE820811105E}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06472E9B-E389-4096-BBBD-4F84E745F017}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A04B49EB-503E-4B4D-A53E-A814963F50D5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B166806-E1BA-4662-AAAA-802A0E38DF76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBCB5163-99D0-4737-B612-A9C3C829C738}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F279D038-D31F-4728-9633-DE820811105E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE21CA78-7A36-4A4D-A583-215F141FBA21}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1652,13 +1652,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A04B49EB-503E-4B4D-A53E-A814963F50D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F3BDB33-B552-49E1-91AC-A4481AD164F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBCB5163-99D0-4737-B612-A9C3C829C738}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D15F862-A2A1-4FFE-A1E5-0123A1ECB773}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE21CA78-7A36-4A4D-A583-215F141FBA21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFADFC7C-AA40-41D3-87CC-9EDC06001DB0}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -392,20 +392,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Dexterity</t>
+          <t>Arboreality</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Arboreality</t>
+          <t>Diet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Diet</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Hand–eye</t>
         </is>
@@ -438,12 +433,9 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
     </row>
@@ -476,15 +468,12 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
     </row>
@@ -512,7 +501,7 @@
         <v>28</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -520,9 +509,6 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -553,15 +539,12 @@
         <v>53</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
         <v>2</v>
       </c>
     </row>
@@ -594,15 +577,12 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
         <v>2</v>
       </c>
     </row>
@@ -635,15 +615,12 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
         <v>1</v>
       </c>
     </row>
@@ -671,15 +648,12 @@
         <v>42</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8">
         <v>0</v>
       </c>
     </row>
@@ -712,15 +686,12 @@
         <v>51</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>4</v>
-      </c>
-      <c r="K9">
         <v>2</v>
       </c>
     </row>
@@ -753,15 +724,12 @@
         <v>17</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10">
         <v>1</v>
       </c>
     </row>
@@ -794,15 +762,12 @@
         <v>39</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
         <v>2</v>
       </c>
     </row>
@@ -830,15 +795,12 @@
         <v>53</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
         <v>2</v>
       </c>
     </row>
@@ -866,15 +828,12 @@
         <v>53</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
         <v>2</v>
       </c>
     </row>
@@ -907,15 +866,12 @@
         <v>53</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>2</v>
-      </c>
-      <c r="K14">
         <v>2</v>
       </c>
     </row>
@@ -943,15 +899,12 @@
         <v>25</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
         <v>1</v>
       </c>
     </row>
@@ -979,15 +932,12 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
         <v>2</v>
       </c>
     </row>
@@ -1020,15 +970,12 @@
         <v>53</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17">
         <v>2</v>
       </c>
     </row>
@@ -1056,15 +1003,12 @@
         <v>43</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
         <v>1</v>
       </c>
     </row>
@@ -1095,12 +1039,9 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19">
         <v>2</v>
       </c>
     </row>
@@ -1128,15 +1069,12 @@
         <v>62</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>2</v>
       </c>
       <c r="J20">
-        <v>2</v>
-      </c>
-      <c r="K20">
         <v>2</v>
       </c>
     </row>
@@ -1169,15 +1107,12 @@
         <v>26</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
         <v>1</v>
       </c>
     </row>
@@ -1208,12 +1143,9 @@
         <v>4</v>
       </c>
       <c r="I22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>2</v>
-      </c>
-      <c r="K22">
         <v>2</v>
       </c>
     </row>
@@ -1246,15 +1178,12 @@
         <v>64</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
         <v>2</v>
       </c>
     </row>
@@ -1282,15 +1211,12 @@
         <v>65</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
         <v>1</v>
       </c>
     </row>
@@ -1318,15 +1244,12 @@
         <v>44</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
         <v>1</v>
       </c>
     </row>
@@ -1359,15 +1282,12 @@
         <v>61</v>
       </c>
       <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
         <v>3</v>
       </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
       <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
         <v>1</v>
       </c>
     </row>
@@ -1652,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F3BDB33-B552-49E1-91AC-A4481AD164F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98EAA8CA-F47A-4310-9E85-CF09645EA0EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D15F862-A2A1-4FFE-A1E5-0123A1ECB773}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B50923-7751-4128-AD31-9C5A21D7C3CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFADFC7C-AA40-41D3-87CC-9EDC06001DB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AD8200-CDB4-4366-8C63-3E81125AF66C}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1294,291 +1294,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD106C4-7107-4436-8ABD-B47F6CDD2DB7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7529F92-5A01-4285-A306-F999AE206C52}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B85948E2-E314-4DE8-BF1D-15145C7317D4}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1294,4 +1294,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A5EB86-22B3-453D-9D86-86DCABD86FE6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F210D0-4990-485D-A2B1-61DEC0DC1220}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE61E43-2106-4D31-AC8F-CC3B4CBB6CDF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1A5EB86-22B3-453D-9D86-86DCABD86FE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115BC1E5-EA54-405B-B462-A41091A703DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F210D0-4990-485D-A2B1-61DEC0DC1220}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E329FD5D-E5C9-4634-A7E7-F96A7B766132}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE61E43-2106-4D31-AC8F-CC3B4CBB6CDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB71F9C8-A8B7-404C-9973-CB88E2C9B346}"/>
 </file>